--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512415_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512415_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.887700000000001</v>
+        <v>8.463699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9493</v>
+        <v>4.5411</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9384</v>
+        <v>3.9225</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9707</v>
+        <v>4.9738</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6222</v>
+        <v>1.621</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3485</v>
+        <v>3.3528</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9419</v>
+        <v>4.0155</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8702</v>
+        <v>0.9074</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0717</v>
+        <v>3.1081</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0287</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.752</v>
+        <v>0.7136</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2768</v>
+        <v>0.2446</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7569</v>
+        <v>0.32</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6946</v>
+        <v>-1.215</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4515</v>
+        <v>1.5349</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3165</v>
+        <v>1.3479</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9068</v>
+        <v>1.943</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.623</v>
+        <v>3.9856</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0387</v>
+        <v>2.3468</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5843</v>
+        <v>1.6388</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0868</v>
+        <v>4.0956</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1214</v>
+        <v>2.1342</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9654</v>
+        <v>1.9614</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5729</v>
+        <v>4.6447</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3971</v>
+        <v>1.4408</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1757</v>
+        <v>3.2039</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4861</v>
+        <v>-0.5491</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7242</v>
+        <v>0.6934</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2103</v>
+        <v>-1.2425</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8735</v>
+        <v>-1.5148</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.441</v>
+        <v>-1.2409</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4325</v>
+        <v>-0.274</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1359</v>
+        <v>0.1577</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5328</v>
+        <v>1.9374</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7132</v>
+        <v>2.6852</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1804</v>
+        <v>-0.7477</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6049</v>
+        <v>3.3823</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9262</v>
+        <v>-1.9759</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.5311</v>
+        <v>5.3582</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5157</v>
+        <v>4.2271</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7907</v>
+        <v>-1.9584</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.275</v>
+        <v>6.1855</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1205</v>
+        <v>-0.8448</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8645</v>
+        <v>-0.0175</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2561</v>
+        <v>-0.8273</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4541</v>
+        <v>-0.3032</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1975</v>
+        <v>-0.5782</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2566</v>
+        <v>0.275</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7262</v>
+        <v>-0.9393</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7262</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0727</v>
+        <v>1.0919</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4296</v>
+        <v>1.3873</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3569</v>
+        <v>-0.2954</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3874</v>
+        <v>0.6145</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9597</v>
+        <v>0.2376</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3471</v>
+        <v>0.3769</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1524</v>
+        <v>1.3077</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9869</v>
+        <v>0.6717</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1394</v>
+        <v>0.6361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7651</v>
+        <v>-0.6932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0272</v>
+        <v>-0.4341</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7922</v>
+        <v>-0.2591</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2291</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1713</v>
+        <v>0.1332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7358</v>
+        <v>0.0796</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4354</v>
+        <v>0.0537</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9385</v>
+        <v>0.3442</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1806</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7781</v>
+        <v>1.0379</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1648</v>
+        <v>-0.3829</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3867</v>
+        <v>1.4208</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6216</v>
+        <v>-1.0038</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2452</v>
+        <v>1.6215</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3764</v>
+        <v>-2.6253</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2958</v>
+        <v>-0.159</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6635</v>
+        <v>1.639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6322</v>
+        <v>-1.798</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6741</v>
+        <v>-0.8448</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4183</v>
+        <v>-0.0175</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2558</v>
+        <v>-0.8273</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.227</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1917</v>
+        <v>-0.124</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.131</v>
+        <v>-0.8793</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0608</v>
+        <v>0.7552</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3482</v>
+        <v>2.9755</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.8823</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3482</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5358000000000001</v>
+        <v>-0.0859</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1792</v>
+        <v>2.1551</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7151</v>
+        <v>-2.2411</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9727</v>
+        <v>-0.6062</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6332</v>
+        <v>1.9367</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6059</v>
+        <v>-2.5429</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2076</v>
+        <v>1.56</v>
       </c>
       <c r="K7" t="n">
-        <v>1.606</v>
+        <v>2.825</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8137</v>
+        <v>-1.2649</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7651</v>
+        <v>-2.1663</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0272</v>
+        <v>-0.8883</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7922</v>
+        <v>-1.278</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8194</v>
+        <v>0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2533</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4339</v>
+        <v>0.4049</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6236</v>
+        <v>0.8682</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5636</v>
+        <v>0.5951</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.2731</v>
       </c>
       <c r="V7" t="n">
-        <v>2.9515</v>
+        <v>-0.7528</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8453</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1062</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4355</v>
+        <v>-1.1227</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1727</v>
+        <v>-1.4426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7372</v>
+        <v>0.3199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0574</v>
+        <v>-0.9334</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0703</v>
+        <v>-1.3252</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0129</v>
+        <v>0.3918</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6245000000000001</v>
+        <v>-0.8521</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3145</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7474</v>
+        <v>-0.1608</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4458</v>
+        <v>-0.4731</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3016</v>
+        <v>0.3122</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6145</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4097</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8783</v>
+        <v>0.645</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4585</v>
+        <v>-0.0866</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4199</v>
+        <v>0.7317</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6625</v>
+        <v>-1.2156</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.022</v>
+        <v>-2.133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3595</v>
+        <v>0.9173</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9369</v>
+        <v>0.0574</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3405</v>
+        <v>1.0676</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4035</v>
+        <v>-1.0101</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.6725</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8941</v>
+        <v>0.6322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.079</v>
+        <v>-1.3047</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1219</v>
+        <v>0.73</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4464</v>
+        <v>0.4354</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3245</v>
+        <v>0.2945</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0485</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.6657</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.4482</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.1423</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.5810999999999999</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.7234</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.1806</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7688</v>
+        <v>-2.3036</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6147</v>
+        <v>-1.5382</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1542</v>
+        <v>-0.7655</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7485</v>
+        <v>-1.7641</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6715</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0877</v>
+        <v>-1.0925</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9937</v>
+        <v>-0.9618</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0227</v>
+        <v>-1.0088</v>
       </c>
       <c r="L10" t="n">
-        <v>0.029</v>
+        <v>0.047</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7548</v>
+        <v>-0.8022</v>
       </c>
       <c r="N10" t="n">
-        <v>0.362</v>
+        <v>0.3373</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1167</v>
+        <v>-1.1395</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3481</v>
+        <v>-0.8635</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1051</v>
+        <v>-1.0782</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.243</v>
+        <v>0.2147</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1421</v>
+        <v>-2.7636</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4719</v>
+        <v>-3.2189</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3299</v>
+        <v>0.4553</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4998</v>
+        <v>-0.511</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1737</v>
+        <v>-1.1854</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6744</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3714</v>
+        <v>-1.3344</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9537</v>
+        <v>-1.938</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6036</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8716</v>
+        <v>0.8234</v>
       </c>
       <c r="N11" t="n">
-        <v>0.78</v>
+        <v>0.7526</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0916</v>
+        <v>0.0708</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8342</v>
+        <v>-1.4188</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1135</v>
+        <v>-0.9207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7207</v>
+        <v>-0.4981</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.421199999999999</v>
+        <v>9.0251</v>
       </c>
       <c r="E12" t="n">
-        <v>2.835100000000001</v>
+        <v>4.399900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5862</v>
+        <v>4.6249</v>
       </c>
       <c r="G12" t="n">
-        <v>8.3611</v>
+        <v>8.305100000000003</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4838</v>
+        <v>3.4606</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8772</v>
+        <v>4.844699999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>11.401</v>
+        <v>11.8547</v>
       </c>
       <c r="K12" t="n">
-        <v>2.094599999999999</v>
+        <v>2.358800000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>9.305999999999999</v>
+        <v>9.4961</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0399</v>
+        <v>-3.5496</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3892</v>
+        <v>1.1018</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.428800000000001</v>
+        <v>-4.6516</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0242</v>
+        <v>1.012299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.218100000000002</v>
+        <v>-9.1104</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2423</v>
+        <v>10.1227</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5674</v>
+        <v>-2.9236</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.626700000000001</v>
+        <v>-5.7724</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0592</v>
+        <v>2.8487</v>
       </c>
       <c r="V12" t="n">
-        <v>2.6032</v>
+        <v>2.6314</v>
       </c>
       <c r="W12" t="n">
-        <v>7.278999999999999</v>
+        <v>7.4278</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.6757</v>
+        <v>-4.7965</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6739</v>
+        <v>4.2391</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4106</v>
+        <v>3.8009</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2633</v>
+        <v>0.4382</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8322</v>
+        <v>1.8684</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7529</v>
+        <v>0.77</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0793</v>
+        <v>1.0983</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1353</v>
+        <v>4.257</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3111</v>
+        <v>1.3802</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8241</v>
+        <v>2.8768</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3031</v>
+        <v>-2.3887</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5583</v>
+        <v>-0.6101</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7448</v>
+        <v>-1.7785</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3648</v>
+        <v>0.108</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0876</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7227</v>
+        <v>1.0048</v>
       </c>
       <c r="V13" t="n">
-        <v>3.4356</v>
+        <v>3.4774</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4356</v>
+        <v>3.4774</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.663</v>
+        <v>1.936</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2789</v>
+        <v>2.3351</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6158</v>
+        <v>-0.3991</v>
       </c>
       <c r="G14" t="n">
-        <v>2.023</v>
+        <v>2.0476</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1503</v>
+        <v>-0.139</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1733</v>
+        <v>2.1865</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6004</v>
+        <v>2.6487</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4568</v>
+        <v>-0.4359</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0572</v>
+        <v>3.0846</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5774</v>
+        <v>-0.6011</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3065</v>
+        <v>0.297</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3775</v>
+        <v>0.6172</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3043</v>
+        <v>0.2698</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0732</v>
+        <v>0.3475</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0924</v>
+        <v>1.4735</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4546</v>
+        <v>1.7232</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3623</v>
+        <v>-0.2497</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3468</v>
+        <v>-0.3036</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1552</v>
+        <v>2.1923</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.502</v>
+        <v>-2.4959</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1198</v>
+        <v>1.2357</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8771</v>
+        <v>1.9531</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7572</v>
+        <v>-0.7174</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4667</v>
+        <v>-1.5393</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2781</v>
+        <v>0.2392</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7448</v>
+        <v>-1.7785</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1859</v>
+        <v>0.5501</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4976</v>
+        <v>-0.3586</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6834</v>
+        <v>0.9087</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5004999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3536</v>
+        <v>-0.2367</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1469</v>
+        <v>0.1257</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0765</v>
+        <v>0.0608</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7388</v>
+        <v>-0.7506</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8153</v>
+        <v>0.8114</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7048</v>
+        <v>0.7186</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5992</v>
+        <v>-0.5933</v>
       </c>
       <c r="L16" t="n">
-        <v>1.304</v>
+        <v>1.3119</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6283</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1396</v>
+        <v>-0.1572</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3179</v>
+        <v>0.7349</v>
       </c>
       <c r="T16" t="n">
-        <v>0.673</v>
+        <v>0.0569</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6448</v>
+        <v>0.678</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8177</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5796</v>
+        <v>-0.4587</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2381</v>
+        <v>-0.1668</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5492</v>
+        <v>-0.5533</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8279</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.326</v>
+        <v>-0.3167</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.326</v>
+        <v>-0.3167</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2232</v>
+        <v>-0.2365</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5019</v>
+        <v>-0.5134</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4734</v>
+        <v>-0.2747</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2536</v>
+        <v>-0.142</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2198</v>
+        <v>-0.1328</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0929</v>
+        <v>-1.5888</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0027</v>
+        <v>-0.7872</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0902</v>
+        <v>-0.8016</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5348</v>
+        <v>-2.2456</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2037</v>
+        <v>-2.4899</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3311</v>
+        <v>0.2443</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5442</v>
+        <v>-0.491</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>-2.2547</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5637</v>
+        <v>1.7637</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9906</v>
+        <v>-1.7546</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2232</v>
+        <v>-0.2352</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7674</v>
+        <v>-1.5194</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>1.4172</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>1.4172</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8646</v>
+        <v>0.6808</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4585</v>
+        <v>-0.5471</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3231</v>
+        <v>1.2279</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8324</v>
+        <v>-1.4411</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8324</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GUEYE</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8005</v>
+        <v>-1.6004</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4053</v>
+        <v>-0.9778</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3952</v>
+        <v>-0.6226</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.507</v>
+        <v>-1.5435</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2154</v>
+        <v>-0.2168</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2916</v>
+        <v>-1.3267</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9722</v>
+        <v>-0.5296</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6577</v>
+        <v>0.0198</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3145</v>
+        <v>-0.5493</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-1.0139</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5577</v>
+        <v>-0.2365</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0229</v>
+        <v>-0.7774</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8194</v>
+        <v>0.4049</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2048</v>
+        <v>0.4049</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4126</v>
+        <v>0.3842</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5895</v>
+        <v>-0.4482</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1768</v>
+        <v>0.8324</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9385</v>
+        <v>-0.846</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2421</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>D. GUEYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.387</v>
+        <v>-2.319</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1331</v>
+        <v>-2.148</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2539</v>
+        <v>-0.1711</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7971</v>
+        <v>-2.512</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6358</v>
+        <v>-1.2251</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4329</v>
+        <v>-1.287</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5892</v>
+        <v>-1.9573</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7199</v>
+        <v>-0.6526</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8693</v>
+        <v>-1.3047</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3863</v>
+        <v>-0.5548</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.5725</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3022</v>
+        <v>0.0177</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8436</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0727</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2291</v>
+        <v>0.2025</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4791</v>
+        <v>0.0636</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6048</v>
+        <v>-0.3687</v>
       </c>
       <c r="U20" t="n">
-        <v>2.084</v>
+        <v>0.4322</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2253</v>
+        <v>0.9393</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.0447</v>
+        <v>1.1902</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4573</v>
+        <v>-4.1474</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1538</v>
+        <v>-3.0044</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3034</v>
+        <v>-1.143</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2467</v>
+        <v>-0.8061</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4754</v>
+        <v>0.6515</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2287</v>
+        <v>-1.4576</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5619</v>
+        <v>1.6431</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2796</v>
+        <v>0.7684</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7177</v>
+        <v>0.8746</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6847</v>
+        <v>-2.4491</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1957</v>
+        <v>-0.1169</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.489</v>
+        <v>-2.3322</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4339</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2219</v>
+        <v>0.7034</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.8339</v>
+        <v>-0.5782</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6121</v>
+        <v>1.2816</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4227</v>
+        <v>-2.2227</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2421</v>
+        <v>-1.0325</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6647</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7957</v>
+        <v>-4.9489</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8095</v>
+        <v>-4.8715</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0137</v>
+        <v>-0.0774</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3112</v>
+        <v>-4.3178</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4161</v>
+        <v>-1.4229</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8951</v>
+        <v>-2.8949</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7054</v>
+        <v>-3.6588</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9974</v>
+        <v>-0.97</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.708</v>
+        <v>-2.6889</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6057</v>
+        <v>-0.6589</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4186</v>
+        <v>-0.4529</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1871</v>
+        <v>-0.206</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8152</v>
+        <v>0.6885</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2889</v>
+        <v>0.164</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5262</v>
+        <v>0.5245</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1191</v>
+        <v>-2.1295</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.393</v>
+        <v>-1.3767</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.4213</v>
+        <v>-7.6924</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5863</v>
+        <v>-4.6251</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.835</v>
+        <v>-3.0674</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.3611</v>
+        <v>-8.305099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4837</v>
+        <v>-3.460599999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.8774</v>
+        <v>-4.844799999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>3.039800000000001</v>
+        <v>3.549699999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3891</v>
+        <v>-1.1017</v>
       </c>
       <c r="L23" t="n">
-        <v>4.4289</v>
+        <v>4.651299999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.4008</v>
+        <v>-11.8547</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0945</v>
+        <v>-2.3585</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.3062</v>
+        <v>-9.4962</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0243</v>
+        <v>-1.0122</v>
       </c>
       <c r="Q23" t="n">
-        <v>-10.2423</v>
+        <v>-10.1227</v>
       </c>
       <c r="R23" t="n">
-        <v>9.2179</v>
+        <v>9.1106</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5675</v>
+        <v>4.256</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0593</v>
+        <v>-2.8488</v>
       </c>
       <c r="U23" t="n">
-        <v>6.626500000000001</v>
+        <v>7.1048</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
       <c r="W23" t="n">
-        <v>4.6757</v>
+        <v>4.7964</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.279</v>
+        <v>-7.4278</v>
       </c>
     </row>
   </sheetData>
